--- a/artfynd/Björnideforsen C artfynd.xlsx
+++ b/artfynd/Björnideforsen C artfynd.xlsx
@@ -36349,7 +36349,7 @@
         <v>119260191</v>
       </c>
       <c r="B354" t="n">
-        <v>92292</v>
+        <v>92325</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
